--- a/review-results/复盘信息抓取-20260829.xlsx
+++ b/review-results/复盘信息抓取-20260829.xlsx
@@ -6184,20 +6184,20 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -6346,56 +6346,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>2387.17</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>17202.78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>1084.75</v>
-      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6442,56 +6402,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2363.69</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>17141.21</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>1007.4</v>
-      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6538,56 +6458,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00:45</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>960</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2363.31</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>16727.19</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>850.6</v>
-      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6634,56 +6514,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2335.77</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>16563.72</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>752.22</v>
-      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6730,56 +6570,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>01:15</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1465</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2340.46</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>265.4</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>17481.1</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>731.64</v>
-      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6826,56 +6626,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>2317.24</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>302.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>17857.19</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>644.88</v>
-      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6922,56 +6682,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>01:45</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1460</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>2292.9</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>302.2</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>17966.85</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>619.25</v>
-      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7018,56 +6738,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1337.7</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>2339.96</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>302.3</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>17215.68</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>602.26</v>
-      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7114,56 +6794,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>02:15</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>842.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>2301.87</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>302.4</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>17866.76</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>526.5700000000001</v>
-      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7210,56 +6850,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>440</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>2353.08</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>17787.37</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>518.0599999999999</v>
-      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7306,56 +6906,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>02:45</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>2369.05</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>496.3</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>17488.32</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>502.43</v>
-      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7402,56 +6962,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>2395.73</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>17211.88</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>470.29</v>
-      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7498,56 +7018,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>2397.26</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>17508.07</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>458.67</v>
-      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7594,56 +7074,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>2377.76</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>17321.57</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>443.17</v>
-      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7690,56 +7130,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>03:45</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2381.52</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>17199.69</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>421.99</v>
-      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7786,56 +7186,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2356.08</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>17053.9</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>407.13</v>
-      </c>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7882,56 +7242,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>2358.55</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>17040</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>420.65</v>
-      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7978,56 +7298,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>2393.06</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>16873.22</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>385.62</v>
-      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8074,56 +7354,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>2392.07</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>16926.07</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>400.96</v>
-      </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8170,56 +7410,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2377.27</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>16999.46</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>443.76</v>
-      </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8266,56 +7466,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>05:15</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>2385.81</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>17127.12</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>452.07</v>
-      </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8362,56 +7522,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2379.22</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>17296.13</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>459.02</v>
-      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8458,56 +7578,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>05:45</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>2383.38</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>17492.57</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>417.25</v>
-      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8554,56 +7634,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>2365.26</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>139.05</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>17990</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>400</v>
-      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8650,56 +7690,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>570</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>2373.38</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>290.87</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>18259.25</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>387.51</v>
-      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8746,56 +7746,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>630</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2379.71</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>577.9299999999999</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>18978.79</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>400.68</v>
-      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8842,56 +7802,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>540</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>2367.53</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>889.03</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>18921.34</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>410.9</v>
-      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8938,56 +7858,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>2403.8</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>1259.95</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>150.9</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>18181.72</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>409.83</v>
-      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9034,56 +7914,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>2414.45</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>1633.95</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>151.1</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>18386.03</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>372.58</v>
-      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9130,56 +7970,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>2453.35</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>2189.83</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>17910.92</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>330.2</v>
-      </c>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9226,56 +8026,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>2467.07</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>2676.07</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>16900.62</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>312.44</v>
-      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9322,56 +8082,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>2537.84</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>3130.42</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>15855.94</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>295.9</v>
-      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9418,56 +8138,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>2582.29</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>3611.5</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>15884.8</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>263.31</v>
-      </c>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9514,56 +8194,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>2593.45</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>4017.15</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>15201.67</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>227.43</v>
-      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9610,56 +8250,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>2633.98</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>4496.22</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>14250.37</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>210.42</v>
-      </c>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="Q36" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9706,56 +8306,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2665.43</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>5187.09</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>12493.81</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>224.47</v>
-      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9802,56 +8362,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-300</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>2730</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5790.02</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>-258.5</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>11402.08</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>246.9</v>
-      </c>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9898,56 +8418,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-840</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2768.53</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>6323.04</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>-260.2</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>11305.22</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>242.39</v>
-      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
       <c r="Q39" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9994,56 +8474,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-1363</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>2829.6</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>6909.32</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>-511</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>10356.39</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>243.87</v>
-      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10090,56 +8530,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-1568</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>2818.59</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>7472.56</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-508.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>9659.1</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>209.55</v>
-      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10186,56 +8586,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-2773</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>2899.08</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>7969.69</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>-509.2</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10399.05</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>198.08</v>
-      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10282,56 +8642,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-3233</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>2950.79</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>8409.68</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>-513.3</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>9883.950000000001</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>186.68</v>
-      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
       <c r="Q43" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10378,56 +8698,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-3483</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>2964.38</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>8705.24</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>-512.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>9600.610000000001</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>194.28</v>
-      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10474,56 +8754,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-3493</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>2945.22</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>8997.76</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>-807.6</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>9628.719999999999</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>183.89</v>
-      </c>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10570,56 +8810,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-3563</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2895.92</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>9258.08</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>-806.3</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>9921.75</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>190.65</v>
-      </c>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10666,56 +8866,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-3658</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>2930.96</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>9183.389999999999</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>-810.8</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>10451.44</v>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>212.04</v>
-      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10762,56 +8922,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-3703</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>2955.26</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>9470.809999999999</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>-809.2</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>10026.45</v>
-      </c>
-      <c r="N48" s="3" t="n">
-        <v>215.28</v>
-      </c>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
       <c r="Q48" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10858,56 +8978,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-3713</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>2931.47</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>9415.120000000001</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>-807.9</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>9714.9</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>223.32</v>
-      </c>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
       <c r="Q49" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10954,56 +9034,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-2933</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>2935.42</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>9470.549999999999</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>-803.2</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="3" t="n">
-        <v>10678.21</v>
-      </c>
-      <c r="N50" s="3" t="n">
-        <v>232.85</v>
-      </c>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11050,56 +9090,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>-2813</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>2926.48</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>9344.620000000001</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>-560.3</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>11064.17</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>235.53</v>
-      </c>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11146,56 +9146,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-2653</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2902.34</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>9231.209999999999</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>-802.2</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>10754.79</v>
-      </c>
-      <c r="N52" s="3" t="n">
-        <v>245.25</v>
-      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="3" t="n"/>
       <c r="Q52" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11242,56 +9202,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-2593</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>2934.98</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>9289.34</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>-802.4</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>10156.72</v>
-      </c>
-      <c r="N53" s="3" t="n">
-        <v>247.56</v>
-      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11338,56 +9258,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-2383</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2930.35</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>9189.690000000001</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>-799.2</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3" t="n">
-        <v>10510.39</v>
-      </c>
-      <c r="N54" s="3" t="n">
-        <v>260.87</v>
-      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="3" t="n"/>
       <c r="Q54" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11434,56 +9314,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-2273</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>2959.54</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>8884.4</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>-800</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="3" t="n">
-        <v>10850.04</v>
-      </c>
-      <c r="N55" s="3" t="n">
-        <v>278.61</v>
-      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="n"/>
       <c r="Q55" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11530,56 +9370,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-1760</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>2911.97</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>8869.84</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>-799.6</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>10592.87</v>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>293.01</v>
-      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="3" t="n"/>
       <c r="Q56" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11626,56 +9426,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-1250</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>2887.73</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>8940.360000000001</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>-551.1</v>
-      </c>
-      <c r="K57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>11171.27</v>
-      </c>
-      <c r="N57" s="3" t="n">
-        <v>276.11</v>
-      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
       <c r="Q57" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11722,56 +9482,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-670</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>2823.84</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>8341.16</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>-795.8</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>10776.12</v>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>294.68</v>
-      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
       <c r="Q58" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11818,56 +9538,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-410</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>2837.68</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>7765.35</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>-795</v>
-      </c>
-      <c r="K59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>11849.75</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>309.89</v>
-      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
       <c r="Q59" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11914,56 +9594,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-90</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>2909.23</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>7548.34</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>-549.9</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>13354.3</v>
-      </c>
-      <c r="N60" s="3" t="n">
-        <v>315.64</v>
-      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12010,56 +9650,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>2886.08</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>7042.14</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>-549.8</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>14322.14</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>326.87</v>
-      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
       <c r="Q61" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12106,56 +9706,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>2839.1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>6380.59</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>-796.7</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>15911.19</v>
-      </c>
-      <c r="N62" s="3" t="n">
-        <v>315.95</v>
-      </c>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12202,56 +9762,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>2820.43</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>5926.63</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>-792.1</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3" t="n">
-        <v>15536.48</v>
-      </c>
-      <c r="N63" s="3" t="n">
-        <v>315.04</v>
-      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
       <c r="Q63" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12298,56 +9818,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>2776.44</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>5272.75</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>-791.5</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>15838.69</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>298.35</v>
-      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="3" t="n"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
+      <c r="M64" s="3" t="n"/>
+      <c r="N64" s="3" t="n"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12394,56 +9874,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>2761.16</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>4682.03</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>-789.8</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>60.15</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>16311.64</v>
-      </c>
-      <c r="N65" s="3" t="n">
-        <v>321.03</v>
-      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12490,56 +9930,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>2722.58</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>4157.06</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>-493.5</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>74.72</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>16295.43</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>338.01</v>
-      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
+      <c r="M66" s="3" t="n"/>
+      <c r="N66" s="3" t="n"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12586,56 +9986,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>520</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>2693.21</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>3745.87</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>74.72</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>16125.94</v>
-      </c>
-      <c r="N67" s="3" t="n">
-        <v>358.56</v>
-      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
+      <c r="M67" s="3" t="n"/>
+      <c r="N67" s="3" t="n"/>
       <c r="Q67" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12682,56 +10042,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>970</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>2724.11</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>3160.46</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>145.71</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="3" t="n">
-        <v>16511.17</v>
-      </c>
-      <c r="N68" s="3" t="n">
-        <v>350.35</v>
-      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="N68" s="3" t="n"/>
       <c r="Q68" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12778,56 +10098,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>1355</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>2695.86</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>2754.07</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>151.9</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>393.76</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>16264.62</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>431.5</v>
-      </c>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
       <c r="Q69" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12874,56 +10154,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>2735</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>2705.4</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>2167.91</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>251.9</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3" t="n">
-        <v>16041.65</v>
-      </c>
-      <c r="N70" s="3" t="n">
-        <v>453.04</v>
-      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
+      <c r="N70" s="3" t="n"/>
       <c r="Q70" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -12970,56 +10210,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>3130</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>2695.81</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>1715.82</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>15101.28</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>457.2</v>
-      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
+      <c r="M71" s="3" t="n"/>
+      <c r="N71" s="3" t="n"/>
       <c r="Q71" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13066,56 +10266,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>3230</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>2658.07</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>1282.09</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>448.5</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="n">
-        <v>14955.92</v>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>413.62</v>
-      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
       <c r="Q72" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13162,56 +10322,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>3167.3</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>2661.85</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>1044.34</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>449.5</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>14478.35</v>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>401.76</v>
-      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
+      <c r="N73" s="3" t="n"/>
       <c r="Q73" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13258,56 +10378,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>2972.3</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>2624.84</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>775.4299999999999</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>550.2</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>14337.69</v>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>403.04</v>
-      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
       <c r="Q74" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13354,56 +10434,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>2860</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>2605.5</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>585.28</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>551.2</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>14855.52</v>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>393.6</v>
-      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
+      <c r="N75" s="3" t="n"/>
       <c r="Q75" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13450,56 +10490,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>2680</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>2594.86</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>378.99</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>15543.19</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>389.37</v>
-      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+      <c r="M76" s="3" t="n"/>
+      <c r="N76" s="3" t="n"/>
       <c r="Q76" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13546,56 +10546,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>2621.39</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>213.75</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>302.9</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>15753.2</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>374.86</v>
-      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
       <c r="Q77" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13642,56 +10602,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>1270</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>2619.89</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>202.95</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>300.5</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>16263.8</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>377.47</v>
-      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+      <c r="M78" s="3" t="n"/>
+      <c r="N78" s="3" t="n"/>
       <c r="Q78" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13738,56 +10658,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>850</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>2599.87</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>216.75</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>300.2</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>16625.82</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>381.25</v>
-      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
       <c r="Q79" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13834,56 +10714,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>2589.37</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>148.2</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>300.4</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>17090.55</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>370.47</v>
-      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+      <c r="M80" s="3" t="n"/>
+      <c r="N80" s="3" t="n"/>
       <c r="Q80" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -13930,56 +10770,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>2610.16</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>142.2</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>16739.58</v>
-      </c>
-      <c r="N81" s="3" t="n">
-        <v>406.66</v>
-      </c>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3" t="n"/>
+      <c r="N81" s="3" t="n"/>
       <c r="Q81" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14026,56 +10826,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>2614.64</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>16683</v>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>430.97</v>
-      </c>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+      <c r="M82" s="3" t="n"/>
+      <c r="N82" s="3" t="n"/>
       <c r="Q82" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14122,56 +10882,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>2654.09</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>16460.45</v>
-      </c>
-      <c r="N83" s="3" t="n">
-        <v>437.75</v>
-      </c>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3" t="n"/>
       <c r="Q83" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14218,56 +10938,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>2658.15</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>15932.29</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>435.86</v>
-      </c>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="N84" s="3" t="n"/>
       <c r="Q84" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14314,56 +10994,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>2674.89</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>100.45</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>16051.82</v>
-      </c>
-      <c r="N85" s="3" t="n">
-        <v>427.64</v>
-      </c>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="3" t="n"/>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+      <c r="M85" s="3" t="n"/>
+      <c r="N85" s="3" t="n"/>
       <c r="Q85" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14410,56 +11050,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>2677.38</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>15960.45</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>460.48</v>
-      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+      <c r="M86" s="3" t="n"/>
+      <c r="N86" s="3" t="n"/>
       <c r="Q86" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14506,56 +11106,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>2672.98</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>16115.6</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>505.52</v>
-      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+      <c r="M87" s="3" t="n"/>
+      <c r="N87" s="3" t="n"/>
       <c r="Q87" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14602,56 +11162,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>2664.79</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>16405.43</v>
-      </c>
-      <c r="N88" s="3" t="n">
-        <v>550.17</v>
-      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+      <c r="M88" s="3" t="n"/>
+      <c r="N88" s="3" t="n"/>
       <c r="Q88" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14698,56 +11218,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>2646.7</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>16360.23</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>566.5700000000001</v>
-      </c>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+      <c r="M89" s="3" t="n"/>
+      <c r="N89" s="3" t="n"/>
       <c r="Q89" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14794,56 +11274,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>2635.56</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>16187.6</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>598.04</v>
-      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+      <c r="M90" s="3" t="n"/>
+      <c r="N90" s="3" t="n"/>
       <c r="Q90" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14890,56 +11330,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>1220</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>2635.16</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>16180.16</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>607.98</v>
-      </c>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="n"/>
+      <c r="N91" s="3" t="n"/>
       <c r="Q91" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14986,56 +11386,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>1520</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>2600.98</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>150.4</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>15947.11</v>
-      </c>
-      <c r="N92" s="3" t="n">
-        <v>622.11</v>
-      </c>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
       <c r="Q92" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15082,56 +11442,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>1620</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>2579.25</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>16370.05</v>
-      </c>
-      <c r="N93" s="3" t="n">
-        <v>635.7</v>
-      </c>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="n"/>
+      <c r="N93" s="3" t="n"/>
       <c r="Q93" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15178,56 +11498,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>2260</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>2537.73</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>251.3</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="n">
-        <v>16263.43</v>
-      </c>
-      <c r="N94" s="3" t="n">
-        <v>667.9400000000001</v>
-      </c>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
       <c r="Q94" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15274,56 +11554,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>2390</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>2535.8</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>250.2</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="3" t="n">
-        <v>15641.33</v>
-      </c>
-      <c r="N95" s="3" t="n">
-        <v>686.76</v>
-      </c>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
+      <c r="N95" s="3" t="n"/>
       <c r="Q95" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15370,56 +11610,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>2537.52</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>151.1</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>15913.32</v>
-      </c>
-      <c r="N96" s="3" t="n">
-        <v>696.5599999999999</v>
-      </c>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+      <c r="M96" s="3" t="n"/>
+      <c r="N96" s="3" t="n"/>
       <c r="Q96" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15466,56 +11666,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>各时段各类电源电量</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>2544.86</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="3" t="n">
-        <v>16646.15</v>
-      </c>
-      <c r="N97" s="3" t="n">
-        <v>715.49</v>
-      </c>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
       <c r="Q97" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -15635,7 +11795,9 @@
       <c r="C2" s="3" t="n">
         <v>27988.4</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>9011.049999999999</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -15660,7 +11822,9 @@
       <c r="C3" s="3" t="n">
         <v>27916.3</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
+        <v>9007.17</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -15685,7 +11849,9 @@
       <c r="C4" s="3" t="n">
         <v>27569.5</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>9003.5</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -15710,7 +11876,9 @@
       <c r="C5" s="3" t="n">
         <v>27777.9</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>9151.719999999999</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -15735,7 +11903,9 @@
       <c r="C6" s="3" t="n">
         <v>30651.1</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>9396.93</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -15760,7 +11930,9 @@
       <c r="C7" s="3" t="n">
         <v>30479.2</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>9492.709999999999</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -15785,7 +11957,9 @@
       <c r="C8" s="3" t="n">
         <v>29780.5</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>9489.67</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -15810,7 +11984,9 @@
       <c r="C9" s="3" t="n">
         <v>29290.8</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>9389.35</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -15835,7 +12011,9 @@
       <c r="C10" s="3" t="n">
         <v>28426.3</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>9135.040000000001</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -15860,7 +12038,9 @@
       <c r="C11" s="3" t="n">
         <v>28193.1</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>8985.42</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -15885,7 +12065,9 @@
       <c r="C12" s="3" t="n">
         <v>27746</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>8984.959999999999</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -15910,7 +12092,9 @@
       <c r="C13" s="3" t="n">
         <v>27537.2</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>8984.459999999999</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -15935,7 +12119,9 @@
       <c r="C14" s="3" t="n">
         <v>27090.8</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>8981.76</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -15960,7 +12146,9 @@
       <c r="C15" s="3" t="n">
         <v>27088.4</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>8981.389999999999</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -15985,7 +12173,9 @@
       <c r="C16" s="3" t="n">
         <v>26784.1</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>8978.209999999999</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -16010,7 +12200,9 @@
       <c r="C17" s="3" t="n">
         <v>26696.8</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>8977.58</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -16035,7 +12227,9 @@
       <c r="C18" s="3" t="n">
         <v>26720</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>8987.370000000001</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -16060,7 +12254,9 @@
       <c r="C19" s="3" t="n">
         <v>26555.6</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>8985.469999999999</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -16085,7 +12281,9 @@
       <c r="C20" s="3" t="n">
         <v>26678.3</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>8981.870000000001</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -16110,7 +12308,9 @@
       <c r="C21" s="3" t="n">
         <v>26531.2</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>8981.91</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -16135,7 +12335,9 @@
       <c r="C22" s="3" t="n">
         <v>26731.3</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>8977.530000000001</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -16160,7 +12362,9 @@
       <c r="C23" s="3" t="n">
         <v>26927.4</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>8979.24</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -16185,7 +12389,9 @@
       <c r="C24" s="3" t="n">
         <v>27454.8</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
+        <v>8982.5</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
@@ -16210,7 +12416,9 @@
       <c r="C25" s="3" t="n">
         <v>27979.2</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>8988.139999999999</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>57.4</v>
       </c>
@@ -16235,7 +12443,9 @@
       <c r="C26" s="3" t="n">
         <v>28966.8</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>8876.360000000001</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>226.8</v>
       </c>
@@ -16260,7 +12470,9 @@
       <c r="C27" s="3" t="n">
         <v>28692.7</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>8441.549999999999</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>449.1</v>
       </c>
@@ -16285,7 +12497,9 @@
       <c r="C28" s="3" t="n">
         <v>28615.2</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>7828.34</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>812.9</v>
       </c>
@@ -16310,7 +12524,9 @@
       <c r="C29" s="3" t="n">
         <v>28241.1</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>7225.5</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>1133</v>
       </c>
@@ -16335,7 +12551,9 @@
       <c r="C30" s="3" t="n">
         <v>28299.3</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>6620.85</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>1497.8</v>
       </c>
@@ -16360,7 +12578,9 @@
       <c r="C31" s="3" t="n">
         <v>28105.7</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>6107.59</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>1817.5</v>
       </c>
@@ -16385,7 +12605,9 @@
       <c r="C32" s="3" t="n">
         <v>28267.4</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>5608.12</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>2106.4</v>
       </c>
@@ -16410,7 +12632,9 @@
       <c r="C33" s="3" t="n">
         <v>28802.3</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>4775.68</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>2474.2</v>
       </c>
@@ -16435,7 +12659,9 @@
       <c r="C34" s="3" t="n">
         <v>29240.9</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>4581.85</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>3166.6</v>
       </c>
@@ -16460,7 +12686,9 @@
       <c r="C35" s="3" t="n">
         <v>29328.4</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>4622.1</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>3815.3</v>
       </c>
@@ -16485,7 +12713,9 @@
       <c r="C36" s="3" t="n">
         <v>28885.1</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>4654.35</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>4530.4</v>
       </c>
@@ -16510,7 +12740,9 @@
       <c r="C37" s="3" t="n">
         <v>28557.5</v>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>4683.82</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>4882.4</v>
       </c>
@@ -16535,7 +12767,9 @@
       <c r="C38" s="3" t="n">
         <v>28532.7</v>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>4707.93</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>5715</v>
       </c>
@@ -16560,7 +12794,9 @@
       <c r="C39" s="3" t="n">
         <v>27415</v>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>4746.84</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>6540.5</v>
       </c>
@@ -16585,7 +12821,9 @@
       <c r="C40" s="3" t="n">
         <v>27244.4</v>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>4778.85</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>7046</v>
       </c>
@@ -16610,7 +12848,9 @@
       <c r="C41" s="3" t="n">
         <v>27072.8</v>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>4796.25</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>7248.7</v>
       </c>
@@ -16635,7 +12875,9 @@
       <c r="C42" s="3" t="n">
         <v>26415.9</v>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>4821.69</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>7773.3</v>
       </c>
@@ -16660,7 +12902,9 @@
       <c r="C43" s="3" t="n">
         <v>26228.2</v>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>4838.07</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>8119</v>
       </c>
@@ -16685,7 +12929,9 @@
       <c r="C44" s="3" t="n">
         <v>26207.1</v>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>4859.67</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>8215.9</v>
       </c>
@@ -16710,7 +12956,9 @@
       <c r="C45" s="3" t="n">
         <v>26748.1</v>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>4876.35</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>8304</v>
       </c>
@@ -16735,7 +12983,9 @@
       <c r="C46" s="3" t="n">
         <v>26888.2</v>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>4882.67</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>8484.200000000001</v>
       </c>
@@ -16760,7 +13010,9 @@
       <c r="C47" s="3" t="n">
         <v>26325.9</v>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>4906.37</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>8472.5</v>
       </c>
@@ -16785,7 +13037,9 @@
       <c r="C48" s="3" t="n">
         <v>25682.5</v>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>4904.87</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>8605.299999999999</v>
       </c>
@@ -16810,7 +13064,9 @@
       <c r="C49" s="3" t="n">
         <v>24785.9</v>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>4902.02</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>8426.5</v>
       </c>
@@ -16835,7 +13091,9 @@
       <c r="C50" s="3" t="n">
         <v>27023</v>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>4911.1</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>8583</v>
       </c>
@@ -16860,7 +13118,9 @@
       <c r="C51" s="3" t="n">
         <v>26792.1</v>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>4902.27</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>8755.799999999999</v>
       </c>
@@ -16885,7 +13145,9 @@
       <c r="C52" s="3" t="n">
         <v>26083.3</v>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>4914.27</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>8471.5</v>
       </c>
@@ -16910,7 +13172,9 @@
       <c r="C53" s="3" t="n">
         <v>26138.9</v>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>4907.39</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>8629</v>
       </c>
@@ -16935,7 +13199,9 @@
       <c r="C54" s="3" t="n">
         <v>26527.2</v>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>4900.48</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>8766.700000000001</v>
       </c>
@@ -16960,7 +13226,9 @@
       <c r="C55" s="3" t="n">
         <v>26820</v>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>4891.88</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>8605.4</v>
       </c>
@@ -16985,7 +13253,9 @@
       <c r="C56" s="3" t="n">
         <v>27560.7</v>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>4880.62</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>7910.9</v>
       </c>
@@ -17010,7 +13280,9 @@
       <c r="C57" s="3" t="n">
         <v>27265.2</v>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>4874.53</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>7749.3</v>
       </c>
@@ -17035,7 +13307,9 @@
       <c r="C58" s="3" t="n">
         <v>27517</v>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>5077.09</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>7264</v>
       </c>
@@ -17060,7 +13334,9 @@
       <c r="C59" s="3" t="n">
         <v>28435</v>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>5338.38</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>6688.6</v>
       </c>
@@ -17085,7 +13361,9 @@
       <c r="C60" s="3" t="n">
         <v>29114.9</v>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>5339.27</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>6253.1</v>
       </c>
@@ -17110,7 +13388,9 @@
       <c r="C61" s="3" t="n">
         <v>29432.8</v>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>5318.48</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>5724.8</v>
       </c>
@@ -17135,7 +13415,9 @@
       <c r="C62" s="3" t="n">
         <v>30062.1</v>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>5286.04</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>5084.6</v>
       </c>
@@ -17160,7 +13442,9 @@
       <c r="C63" s="3" t="n">
         <v>30552.1</v>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>5464.74</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>4732.4</v>
       </c>
@@ -17185,7 +13469,9 @@
       <c r="C64" s="3" t="n">
         <v>31129.6</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>5637.73</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>4717.9</v>
       </c>
@@ -17210,7 +13496,9 @@
       <c r="C65" s="3" t="n">
         <v>31212.2</v>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>5772.16</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>4173.7</v>
       </c>
@@ -17235,7 +13523,9 @@
       <c r="C66" s="3" t="n">
         <v>31586.6</v>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>6022.23</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>4039.8</v>
       </c>
@@ -17260,7 +13550,9 @@
       <c r="C67" s="3" t="n">
         <v>32184.1</v>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>6117.26</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>3348.3</v>
       </c>
@@ -17285,7 +13577,9 @@
       <c r="C68" s="3" t="n">
         <v>32541.9</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>6711.77</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>2953.1</v>
       </c>
@@ -17310,7 +13604,9 @@
       <c r="C69" s="3" t="n">
         <v>33563.4</v>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>7297.05</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>2588</v>
       </c>
@@ -17335,7 +13631,9 @@
       <c r="C70" s="3" t="n">
         <v>33889.8</v>
       </c>
-      <c r="D70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>7889.85</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>2230.1</v>
       </c>
@@ -17360,7 +13658,9 @@
       <c r="C71" s="3" t="n">
         <v>34305</v>
       </c>
-      <c r="D71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>8481.67</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>1854.9</v>
       </c>
@@ -17385,7 +13685,9 @@
       <c r="C72" s="3" t="n">
         <v>34891.1</v>
       </c>
-      <c r="D72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>9070.59</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>1343.8</v>
       </c>
@@ -17410,7 +13712,9 @@
       <c r="C73" s="3" t="n">
         <v>35049.4</v>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>9635.5</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>931.7</v>
       </c>
@@ -17435,7 +13739,9 @@
       <c r="C74" s="3" t="n">
         <v>35238.5</v>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>9980.66</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>584.5</v>
       </c>
@@ -17460,7 +13766,9 @@
       <c r="C75" s="3" t="n">
         <v>35413</v>
       </c>
-      <c r="D75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>9958.309999999999</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>260.1</v>
       </c>
@@ -17485,7 +13793,9 @@
       <c r="C76" s="3" t="n">
         <v>35118.6</v>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>9941.299999999999</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>55.7</v>
       </c>
@@ -17510,7 +13820,9 @@
       <c r="C77" s="3" t="n">
         <v>34993.9</v>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>9931.43</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -17535,7 +13847,9 @@
       <c r="C78" s="3" t="n">
         <v>34853.9</v>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>9921.49</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -17560,7 +13874,9 @@
       <c r="C79" s="3" t="n">
         <v>34995.4</v>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="3" t="n">
+        <v>9919.719999999999</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -17585,7 +13901,9 @@
       <c r="C80" s="3" t="n">
         <v>34418.9</v>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="3" t="n">
+        <v>9920.360000000001</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -17610,7 +13928,9 @@
       <c r="C81" s="3" t="n">
         <v>33826.1</v>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="3" t="n">
+        <v>9822.139999999999</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -17635,7 +13955,9 @@
       <c r="C82" s="3" t="n">
         <v>33916.4</v>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="3" t="n">
+        <v>9567.940000000001</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -17660,7 +13982,9 @@
       <c r="C83" s="3" t="n">
         <v>33357.3</v>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>9417.110000000001</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -17685,7 +14009,9 @@
       <c r="C84" s="3" t="n">
         <v>33518.2</v>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>9417.26</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -17710,7 +14036,9 @@
       <c r="C85" s="3" t="n">
         <v>33300.1</v>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>9416.860000000001</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -17735,7 +14063,9 @@
       <c r="C86" s="3" t="n">
         <v>32939.3</v>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="3" t="n">
+        <v>9408.440000000001</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -17760,7 +14090,9 @@
       <c r="C87" s="3" t="n">
         <v>32399.6</v>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="3" t="n">
+        <v>9413.190000000001</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -17785,7 +14117,9 @@
       <c r="C88" s="3" t="n">
         <v>32052.5</v>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>9418.360000000001</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -17810,7 +14144,9 @@
       <c r="C89" s="3" t="n">
         <v>31683.4</v>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>9423.49</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -17835,7 +14171,9 @@
       <c r="C90" s="3" t="n">
         <v>31413.7</v>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>9378.42</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -17860,7 +14198,9 @@
       <c r="C91" s="3" t="n">
         <v>30987.5</v>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>9384.969999999999</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -17885,7 +14225,9 @@
       <c r="C92" s="3" t="n">
         <v>30675.1</v>
       </c>
-      <c r="D92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>9389.530000000001</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -17910,7 +14252,9 @@
       <c r="C93" s="3" t="n">
         <v>30375.9</v>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>9395.98</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -17935,7 +14279,9 @@
       <c r="C94" s="3" t="n">
         <v>29731.9</v>
       </c>
-      <c r="D94" s="3" t="n"/>
+      <c r="D94" s="3" t="n">
+        <v>9401.49</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -17960,7 +14306,9 @@
       <c r="C95" s="3" t="n">
         <v>29192.5</v>
       </c>
-      <c r="D95" s="3" t="n"/>
+      <c r="D95" s="3" t="n">
+        <v>9405.07</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -17985,7 +14333,9 @@
       <c r="C96" s="3" t="n">
         <v>28482.2</v>
       </c>
-      <c r="D96" s="3" t="n"/>
+      <c r="D96" s="3" t="n">
+        <v>9406.68</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -18010,7 +14360,9 @@
       <c r="C97" s="3" t="n">
         <v>28301.7</v>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>9409.65</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -18112,7 +14464,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>发电总出力</t>
+          <t>日前非市场化机组总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -18138,11 +14490,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>960</v>
+        <v>768</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -18151,42 +14503,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>768</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>日前储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>日前储能充电计划及电价</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>96</v>
-      </c>
-      <c r="C11" t="n">
         <v>9</v>
       </c>
     </row>
+    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260829.xlsx
+++ b/review-results/复盘信息抓取-20260829.xlsx
@@ -6184,20 +6184,20 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -6346,16 +6346,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2387.17</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>17202.78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>1084.75</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6402,16 +6442,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2363.69</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>17141.21</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1007.4</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6458,16 +6538,56 @@
       </c>
     </row>
     <row r="4">
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2363.31</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>16727.19</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>850.6</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6514,16 +6634,56 @@
       </c>
     </row>
     <row r="5">
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2335.77</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>16563.72</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>752.22</v>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6570,16 +6730,56 @@
       </c>
     </row>
     <row r="6">
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1465</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2340.46</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>17481.1</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>731.64</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6626,16 +6826,56 @@
       </c>
     </row>
     <row r="7">
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2317.24</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17857.19</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>644.88</v>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6682,16 +6922,56 @@
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2292.9</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>17966.85</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>619.25</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6738,16 +7018,56 @@
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1337.7</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2339.96</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>302.3</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>17215.68</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>602.26</v>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6794,16 +7114,56 @@
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>842.7</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2301.87</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>17866.76</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>526.5700000000001</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6850,16 +7210,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2353.08</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>17787.37</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>518.0599999999999</v>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6906,16 +7306,56 @@
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2369.05</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>496.3</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17488.32</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>502.43</v>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -6962,16 +7402,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2395.73</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>17211.88</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>470.29</v>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7018,16 +7498,56 @@
       </c>
     </row>
     <row r="14">
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2397.26</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>17508.07</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>458.67</v>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7074,16 +7594,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2377.76</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>17321.57</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>443.17</v>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7130,16 +7690,56 @@
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2381.52</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>17199.69</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>421.99</v>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7186,16 +7786,56 @@
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2356.08</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>17053.9</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>407.13</v>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7242,16 +7882,56 @@
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2358.55</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>17040</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>420.65</v>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7298,16 +7978,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2393.06</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>16873.22</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>385.62</v>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7354,16 +8074,56 @@
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2392.07</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>16926.07</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>400.96</v>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7410,16 +8170,56 @@
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2377.27</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>16999.46</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>443.76</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7466,16 +8266,56 @@
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2385.81</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>17127.12</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>452.07</v>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7522,16 +8362,56 @@
       </c>
     </row>
     <row r="23">
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2379.22</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>17296.13</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>459.02</v>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7578,16 +8458,56 @@
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2383.38</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>17492.57</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>417.25</v>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7634,16 +8554,56 @@
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2365.26</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>17990</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>400</v>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7690,16 +8650,56 @@
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2373.38</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>290.87</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>18259.25</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>387.51</v>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7746,16 +8746,56 @@
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>630</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2379.71</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>577.9299999999999</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>18978.79</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>400.68</v>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7802,16 +8842,56 @@
       </c>
     </row>
     <row r="28">
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>540</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2367.53</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>889.03</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>18921.34</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>410.9</v>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7858,16 +8938,56 @@
       </c>
     </row>
     <row r="29">
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2403.8</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1259.95</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>18181.72</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>409.83</v>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7914,16 +9034,56 @@
       </c>
     </row>
     <row r="30">
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2414.45</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1633.95</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>18386.03</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>372.58</v>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -7970,16 +9130,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2453.35</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>2189.83</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>17910.92</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>330.2</v>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8026,16 +9226,56 @@
       </c>
     </row>
     <row r="32">
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2467.07</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>2676.07</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16900.62</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>312.44</v>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8082,16 +9322,56 @@
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2537.84</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>3130.42</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>15855.94</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>295.9</v>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8138,16 +9418,56 @@
       </c>
     </row>
     <row r="34">
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2582.29</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>3611.5</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>15884.8</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>263.31</v>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8194,16 +9514,56 @@
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2593.45</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>4017.15</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>15201.67</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>227.43</v>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8250,16 +9610,56 @@
       </c>
     </row>
     <row r="36">
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2633.98</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>4496.22</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>14250.37</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>210.42</v>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8306,16 +9706,56 @@
       </c>
     </row>
     <row r="37">
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2665.43</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>5187.09</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>12493.81</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>224.47</v>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8362,16 +9802,56 @@
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-300</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>5790.02</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>-258.5</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>11402.08</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>246.9</v>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8418,16 +9898,56 @@
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-840</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2768.53</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>6323.04</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>-260.2</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>11305.22</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>242.39</v>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8474,16 +9994,56 @@
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-1363</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2829.6</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>6909.32</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>-511</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>10356.39</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>243.87</v>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8530,16 +10090,56 @@
       </c>
     </row>
     <row r="41">
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-1568</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2818.59</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>7472.56</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-508.9</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>9659.1</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>209.55</v>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8586,16 +10186,56 @@
       </c>
     </row>
     <row r="42">
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-2773</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2899.08</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>7969.69</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>-509.2</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10399.05</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>198.08</v>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8642,16 +10282,56 @@
       </c>
     </row>
     <row r="43">
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-3233</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2950.79</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>8409.68</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>-513.3</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>9883.950000000001</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>186.68</v>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8698,16 +10378,56 @@
       </c>
     </row>
     <row r="44">
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-3483</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2964.38</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>8705.24</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>-512.2</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>9600.610000000001</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>194.28</v>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8754,16 +10474,56 @@
       </c>
     </row>
     <row r="45">
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-3493</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2945.22</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>8997.76</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>-807.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>9628.719999999999</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>183.89</v>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8810,16 +10570,56 @@
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-3563</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2895.92</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>9258.08</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-806.3</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>9921.75</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>190.65</v>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8866,16 +10666,56 @@
       </c>
     </row>
     <row r="47">
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-3658</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2930.96</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>9183.389999999999</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>-810.8</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>10451.44</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>212.04</v>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8922,16 +10762,56 @@
       </c>
     </row>
     <row r="48">
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-3703</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2955.26</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>9470.809999999999</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>-809.2</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>10026.45</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>215.28</v>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -8978,16 +10858,56 @@
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="3" t="n"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-3713</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2931.47</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>9415.120000000001</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>-807.9</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>9714.9</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>223.32</v>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9034,16 +10954,56 @@
       </c>
     </row>
     <row r="50">
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-2933</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2935.42</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>9470.549999999999</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>-803.2</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>10678.21</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>232.85</v>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9090,16 +11050,56 @@
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="n"/>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-2813</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2926.48</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>9344.620000000001</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>-560.3</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>11064.17</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>235.53</v>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9146,16 +11146,56 @@
       </c>
     </row>
     <row r="52">
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="n"/>
-      <c r="L52" s="3" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="N52" s="3" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-2653</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2902.34</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>9231.209999999999</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>-802.2</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>10754.79</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>245.25</v>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9202,16 +11242,56 @@
       </c>
     </row>
     <row r="53">
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="n"/>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-2593</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2934.98</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>9289.34</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>-802.4</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>10156.72</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>247.56</v>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9258,16 +11338,56 @@
       </c>
     </row>
     <row r="54">
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="n"/>
-      <c r="L54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-2383</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2930.35</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>9189.690000000001</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>-799.2</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>10510.39</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>260.87</v>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9314,16 +11434,56 @@
       </c>
     </row>
     <row r="55">
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="n"/>
-      <c r="L55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-2273</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2959.54</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>8884.4</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>-800</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>10850.04</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>278.61</v>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9370,16 +11530,56 @@
       </c>
     </row>
     <row r="56">
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-1760</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2911.97</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>8869.84</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>-799.6</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>10592.87</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>293.01</v>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9426,16 +11626,56 @@
       </c>
     </row>
     <row r="57">
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2887.73</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>8940.360000000001</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>-551.1</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>11171.27</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>276.11</v>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9482,16 +11722,56 @@
       </c>
     </row>
     <row r="58">
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="n"/>
-      <c r="L58" s="3" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="3" t="n"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-670</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2823.84</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>8341.16</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>-795.8</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>10776.12</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>294.68</v>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9538,16 +11818,56 @@
       </c>
     </row>
     <row r="59">
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
-      <c r="J59" s="3" t="n"/>
-      <c r="K59" s="3" t="n"/>
-      <c r="L59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-410</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2837.68</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>7765.35</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>-795</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>11849.75</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>309.89</v>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9594,16 +11914,56 @@
       </c>
     </row>
     <row r="60">
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2909.23</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>7548.34</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>-549.9</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>13354.3</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>315.64</v>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9650,16 +12010,56 @@
       </c>
     </row>
     <row r="61">
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="n"/>
-      <c r="L61" s="3" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="3" t="n"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2886.08</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>7042.14</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>-549.8</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>14322.14</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>326.87</v>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9706,16 +12106,56 @@
       </c>
     </row>
     <row r="62">
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="n"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2839.1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>6380.59</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>-796.7</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>15911.19</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>315.95</v>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9762,16 +12202,56 @@
       </c>
     </row>
     <row r="63">
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="n"/>
-      <c r="L63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="3" t="n"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2820.43</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>5926.63</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>-792.1</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>15536.48</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>315.04</v>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9818,16 +12298,56 @@
       </c>
     </row>
     <row r="64">
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="3" t="n"/>
-      <c r="L64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="3" t="n"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>2776.44</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>5272.75</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>-791.5</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>15838.69</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>298.35</v>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9874,16 +12394,56 @@
       </c>
     </row>
     <row r="65">
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
-      <c r="J65" s="3" t="n"/>
-      <c r="K65" s="3" t="n"/>
-      <c r="L65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="3" t="n"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2761.16</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>4682.03</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>-789.8</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>16311.64</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>321.03</v>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9930,16 +12490,56 @@
       </c>
     </row>
     <row r="66">
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="n"/>
-      <c r="L66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="3" t="n"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2722.58</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>4157.06</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>-493.5</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>16295.43</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>338.01</v>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -9986,16 +12586,56 @@
       </c>
     </row>
     <row r="67">
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
-      <c r="J67" s="3" t="n"/>
-      <c r="K67" s="3" t="n"/>
-      <c r="L67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="3" t="n"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>2693.21</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>3745.87</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>16125.94</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>358.56</v>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10042,16 +12682,56 @@
       </c>
     </row>
     <row r="68">
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>970</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>2724.11</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>3160.46</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>145.71</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>16511.17</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>350.35</v>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10098,16 +12778,56 @@
       </c>
     </row>
     <row r="69">
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="3" t="n"/>
-      <c r="L69" s="3" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="N69" s="3" t="n"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1355</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2695.86</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>2754.07</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>393.76</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>16264.62</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>431.5</v>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10154,16 +12874,56 @@
       </c>
     </row>
     <row r="70">
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="3" t="n"/>
-      <c r="K70" s="3" t="n"/>
-      <c r="L70" s="3" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="N70" s="3" t="n"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>2735</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2705.4</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>2167.91</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>251.9</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>16041.65</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>453.04</v>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10210,16 +12970,56 @@
       </c>
     </row>
     <row r="71">
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="n"/>
-      <c r="L71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
-      <c r="N71" s="3" t="n"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>3130</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2695.81</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>1715.82</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>15101.28</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>457.2</v>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10266,16 +13066,56 @@
       </c>
     </row>
     <row r="72">
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>3230</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>2658.07</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>1282.09</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>448.5</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>14955.92</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>413.62</v>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10322,16 +13162,56 @@
       </c>
     </row>
     <row r="73">
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3167.3</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2661.85</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>1044.34</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>14478.35</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>401.76</v>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10378,16 +13258,56 @@
       </c>
     </row>
     <row r="74">
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="N74" s="3" t="n"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>2972.3</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2624.84</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>775.4299999999999</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>550.2</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>14337.69</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>403.04</v>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10434,16 +13354,56 @@
       </c>
     </row>
     <row r="75">
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="n"/>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2605.5</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>585.28</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>551.2</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>14855.52</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>393.6</v>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10490,16 +13450,56 @@
       </c>
     </row>
     <row r="76">
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="3" t="n"/>
-      <c r="L76" s="3" t="n"/>
-      <c r="M76" s="3" t="n"/>
-      <c r="N76" s="3" t="n"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2680</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2594.86</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>378.99</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>15543.19</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>389.37</v>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10546,16 +13546,56 @@
       </c>
     </row>
     <row r="77">
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2621.39</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>15753.2</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>374.86</v>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10602,16 +13642,56 @@
       </c>
     </row>
     <row r="78">
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1270</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2619.89</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>202.95</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>16263.8</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>377.47</v>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10658,16 +13738,56 @@
       </c>
     </row>
     <row r="79">
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="n"/>
-      <c r="L79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
-      <c r="N79" s="3" t="n"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2599.87</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>216.75</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>16625.82</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>381.25</v>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10714,16 +13834,56 @@
       </c>
     </row>
     <row r="80">
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2589.37</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>17090.55</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>370.47</v>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10770,16 +13930,56 @@
       </c>
     </row>
     <row r="81">
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="n"/>
-      <c r="L81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
-      <c r="N81" s="3" t="n"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2610.16</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>16739.58</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>406.66</v>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10826,16 +14026,56 @@
       </c>
     </row>
     <row r="82">
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="3" t="n"/>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="3" t="n"/>
-      <c r="L82" s="3" t="n"/>
-      <c r="M82" s="3" t="n"/>
-      <c r="N82" s="3" t="n"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2614.64</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>16683</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>430.97</v>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10882,16 +14122,56 @@
       </c>
     </row>
     <row r="83">
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="n"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2654.09</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>16460.45</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>437.75</v>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10938,16 +14218,56 @@
       </c>
     </row>
     <row r="84">
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="3" t="n"/>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="N84" s="3" t="n"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>2658.15</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>15932.29</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>435.86</v>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -10994,16 +14314,56 @@
       </c>
     </row>
     <row r="85">
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="3" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="n"/>
-      <c r="L85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
-      <c r="N85" s="3" t="n"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2674.89</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>16051.82</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>427.64</v>
+      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11050,16 +14410,56 @@
       </c>
     </row>
     <row r="86">
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="n"/>
-      <c r="L86" s="3" t="n"/>
-      <c r="M86" s="3" t="n"/>
-      <c r="N86" s="3" t="n"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2677.38</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>15960.45</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>460.48</v>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11106,16 +14506,56 @@
       </c>
     </row>
     <row r="87">
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="n"/>
-      <c r="L87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
-      <c r="N87" s="3" t="n"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2672.98</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>16115.6</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>505.52</v>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11162,16 +14602,56 @@
       </c>
     </row>
     <row r="88">
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="N88" s="3" t="n"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2664.79</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>16405.43</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>550.17</v>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11218,16 +14698,56 @@
       </c>
     </row>
     <row r="89">
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="n"/>
-      <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
-      <c r="N89" s="3" t="n"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>2646.7</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>16360.23</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>566.5700000000001</v>
+      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11274,16 +14794,56 @@
       </c>
     </row>
     <row r="90">
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="n"/>
-      <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>2635.56</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>16187.6</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>598.04</v>
+      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11330,16 +14890,56 @@
       </c>
     </row>
     <row r="91">
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="n"/>
-      <c r="I91" s="3" t="n"/>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="n"/>
-      <c r="L91" s="3" t="n"/>
-      <c r="M91" s="3" t="n"/>
-      <c r="N91" s="3" t="n"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>1220</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2635.16</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>16180.16</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>607.98</v>
+      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11386,16 +14986,56 @@
       </c>
     </row>
     <row r="92">
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="n"/>
-      <c r="L92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
-      <c r="N92" s="3" t="n"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2600.98</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>15947.11</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>622.11</v>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11442,16 +15082,56 @@
       </c>
     </row>
     <row r="93">
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="N93" s="3" t="n"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>2579.25</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>16370.05</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>635.7</v>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11498,16 +15178,56 @@
       </c>
     </row>
     <row r="94">
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="n"/>
-      <c r="L94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
-      <c r="N94" s="3" t="n"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>2537.73</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>251.3</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="n">
+        <v>16263.43</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>667.9400000000001</v>
+      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11554,16 +15274,56 @@
       </c>
     </row>
     <row r="95">
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="n"/>
-      <c r="L95" s="3" t="n"/>
-      <c r="M95" s="3" t="n"/>
-      <c r="N95" s="3" t="n"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>2535.8</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>15641.33</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>686.76</v>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11610,16 +15370,56 @@
       </c>
     </row>
     <row r="96">
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="n"/>
-      <c r="L96" s="3" t="n"/>
-      <c r="M96" s="3" t="n"/>
-      <c r="N96" s="3" t="n"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>2537.52</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>15913.32</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>696.5599999999999</v>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -11666,16 +15466,56 @@
       </c>
     </row>
     <row r="97">
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="n"/>
-      <c r="L97" s="3" t="n"/>
-      <c r="M97" s="3" t="n"/>
-      <c r="N97" s="3" t="n"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>各时段各类电源电量</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>2544.86</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>16646.15</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>715.49</v>
+      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>各时段各类电源的开机台数</t>
@@ -14490,11 +18330,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>768</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -14503,30 +18343,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日前储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260829.xlsx
+++ b/review-results/复盘信息抓取-20260829.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18227,9 +18222,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
